--- a/database/event/6869/raw_event_6869_data.xlsx
+++ b/database/event/6869/raw_event_6869_data.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,58 +413,118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J221"/>
+  <dimension ref="A1:V221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>team_avg_rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>match_baseline_rating</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>map_kpr</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>map_dpr</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>map_kast</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>map_mk_rating</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>map_swing_total</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>map_adr</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>map_rating30</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>map_kprw</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>map_swing_added</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>map_swing_given</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>map_kills</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>map_won_kills</t>
         </is>
       </c>
     </row>
@@ -519,6 +567,42 @@
       <c r="J2" t="n">
         <v>1.074</v>
       </c>
+      <c r="K2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M2" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="O2" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="P2" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="S2" t="n">
+        <v>300.85</v>
+      </c>
+      <c r="T2" t="n">
+        <v>160.82</v>
+      </c>
+      <c r="U2" t="n">
+        <v>15</v>
+      </c>
+      <c r="V2" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -559,6 +643,42 @@
       <c r="J3" t="n">
         <v>1.074</v>
       </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P3" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>235.54</v>
+      </c>
+      <c r="T3" t="n">
+        <v>197.32</v>
+      </c>
+      <c r="U3" t="n">
+        <v>17</v>
+      </c>
+      <c r="V3" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -599,6 +719,42 @@
       <c r="J4" t="n">
         <v>1.074</v>
       </c>
+      <c r="K4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M4" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P4" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="S4" t="n">
+        <v>204.19</v>
+      </c>
+      <c r="T4" t="n">
+        <v>167.87</v>
+      </c>
+      <c r="U4" t="n">
+        <v>13</v>
+      </c>
+      <c r="V4" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -639,6 +795,42 @@
       <c r="J5" t="n">
         <v>1.074</v>
       </c>
+      <c r="K5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M5" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="P5" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="S5" t="n">
+        <v>255.76</v>
+      </c>
+      <c r="T5" t="n">
+        <v>163.64</v>
+      </c>
+      <c r="U5" t="n">
+        <v>12</v>
+      </c>
+      <c r="V5" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -679,6 +871,42 @@
       <c r="J6" t="n">
         <v>1.074</v>
       </c>
+      <c r="K6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M6" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="P6" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="S6" t="n">
+        <v>159.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>121.67</v>
+      </c>
+      <c r="U6" t="n">
+        <v>12</v>
+      </c>
+      <c r="V6" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -719,6 +947,42 @@
       <c r="J7" t="n">
         <v>1.074</v>
       </c>
+      <c r="K7" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M7" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="P7" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>259.87</v>
+      </c>
+      <c r="T7" t="n">
+        <v>283.78</v>
+      </c>
+      <c r="U7" t="n">
+        <v>17</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -759,6 +1023,42 @@
       <c r="J8" t="n">
         <v>1.074</v>
       </c>
+      <c r="K8" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M8" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="P8" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>142.72</v>
+      </c>
+      <c r="T8" t="n">
+        <v>204.82</v>
+      </c>
+      <c r="U8" t="n">
+        <v>10</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -799,6 +1099,42 @@
       <c r="J9" t="n">
         <v>1.074</v>
       </c>
+      <c r="K9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M9" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-3.64</v>
+      </c>
+      <c r="P9" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>145.02</v>
+      </c>
+      <c r="T9" t="n">
+        <v>210.52</v>
+      </c>
+      <c r="U9" t="n">
+        <v>9</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -839,6 +1175,42 @@
       <c r="J10" t="n">
         <v>1.074</v>
       </c>
+      <c r="K10" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M10" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="P10" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>156.25</v>
+      </c>
+      <c r="T10" t="n">
+        <v>250.56</v>
+      </c>
+      <c r="U10" t="n">
+        <v>10</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -879,6 +1251,42 @@
       <c r="J11" t="n">
         <v>1.074</v>
       </c>
+      <c r="K11" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M11" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-5.47</v>
+      </c>
+      <c r="P11" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S11" t="n">
+        <v>107.46</v>
+      </c>
+      <c r="T11" t="n">
+        <v>205.86</v>
+      </c>
+      <c r="U11" t="n">
+        <v>7</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -919,6 +1327,42 @@
       <c r="J12" t="n">
         <v>1.063</v>
       </c>
+      <c r="K12" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M12" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="P12" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="S12" t="n">
+        <v>214.57</v>
+      </c>
+      <c r="T12" t="n">
+        <v>106.61</v>
+      </c>
+      <c r="U12" t="n">
+        <v>14</v>
+      </c>
+      <c r="V12" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -959,6 +1403,42 @@
       <c r="J13" t="n">
         <v>1.063</v>
       </c>
+      <c r="K13" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M13" t="n">
+        <v>100</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O13" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="P13" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="S13" t="n">
+        <v>212.72</v>
+      </c>
+      <c r="T13" t="n">
+        <v>78.17</v>
+      </c>
+      <c r="U13" t="n">
+        <v>13</v>
+      </c>
+      <c r="V13" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -999,6 +1479,42 @@
       <c r="J14" t="n">
         <v>1.063</v>
       </c>
+      <c r="K14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M14" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="P14" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="S14" t="n">
+        <v>216.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>149.07</v>
+      </c>
+      <c r="U14" t="n">
+        <v>16</v>
+      </c>
+      <c r="V14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1039,6 +1555,42 @@
       <c r="J15" t="n">
         <v>1.063</v>
       </c>
+      <c r="K15" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M15" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P15" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="S15" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>109.87</v>
+      </c>
+      <c r="U15" t="n">
+        <v>13</v>
+      </c>
+      <c r="V15" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1079,6 +1631,42 @@
       <c r="J16" t="n">
         <v>1.063</v>
       </c>
+      <c r="K16" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M16" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="P16" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="S16" t="n">
+        <v>108.21</v>
+      </c>
+      <c r="T16" t="n">
+        <v>157.62</v>
+      </c>
+      <c r="U16" t="n">
+        <v>11</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1111,7 +1699,7 @@
         <v>1.48</v>
       </c>
       <c r="H17" t="n">
-        <v>0.676</v>
+        <v>0.6759999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>17</v>
@@ -1119,6 +1707,42 @@
       <c r="J17" t="n">
         <v>1.063</v>
       </c>
+      <c r="K17" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M17" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="O17" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="P17" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>244.59</v>
+      </c>
+      <c r="T17" t="n">
+        <v>158.61</v>
+      </c>
+      <c r="U17" t="n">
+        <v>15</v>
+      </c>
+      <c r="V17" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1151,7 +1775,7 @@
         <v>0.72</v>
       </c>
       <c r="H18" t="n">
-        <v>0.676</v>
+        <v>0.6759999999999999</v>
       </c>
       <c r="I18" t="n">
         <v>17</v>
@@ -1159,6 +1783,42 @@
       <c r="J18" t="n">
         <v>1.063</v>
       </c>
+      <c r="K18" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M18" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-3.32</v>
+      </c>
+      <c r="P18" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S18" t="n">
+        <v>144.62</v>
+      </c>
+      <c r="T18" t="n">
+        <v>201.02</v>
+      </c>
+      <c r="U18" t="n">
+        <v>9</v>
+      </c>
+      <c r="V18" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1191,7 +1851,7 @@
         <v>0.54</v>
       </c>
       <c r="H19" t="n">
-        <v>0.676</v>
+        <v>0.6759999999999999</v>
       </c>
       <c r="I19" t="n">
         <v>17</v>
@@ -1199,6 +1859,42 @@
       <c r="J19" t="n">
         <v>1.063</v>
       </c>
+      <c r="K19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M19" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-4.12</v>
+      </c>
+      <c r="P19" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>78.59</v>
+      </c>
+      <c r="T19" t="n">
+        <v>148.67</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1231,7 +1927,7 @@
         <v>0.45</v>
       </c>
       <c r="H20" t="n">
-        <v>0.676</v>
+        <v>0.6759999999999999</v>
       </c>
       <c r="I20" t="n">
         <v>17</v>
@@ -1239,6 +1935,42 @@
       <c r="J20" t="n">
         <v>1.063</v>
       </c>
+      <c r="K20" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M20" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-4.54</v>
+      </c>
+      <c r="P20" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>91</v>
+      </c>
+      <c r="T20" t="n">
+        <v>168.22</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1271,7 +2003,7 @@
         <v>0.19</v>
       </c>
       <c r="H21" t="n">
-        <v>0.676</v>
+        <v>0.6759999999999999</v>
       </c>
       <c r="I21" t="n">
         <v>17</v>
@@ -1279,6 +2011,42 @@
       <c r="J21" t="n">
         <v>1.063</v>
       </c>
+      <c r="K21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="P21" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="T21" t="n">
+        <v>204.51</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1319,6 +2087,42 @@
       <c r="J22" t="n">
         <v>1.037</v>
       </c>
+      <c r="K22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M22" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O22" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="P22" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.474</v>
+      </c>
+      <c r="S22" t="n">
+        <v>539.48</v>
+      </c>
+      <c r="T22" t="n">
+        <v>322.65</v>
+      </c>
+      <c r="U22" t="n">
+        <v>36</v>
+      </c>
+      <c r="V22" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1359,6 +2163,42 @@
       <c r="J23" t="n">
         <v>1.037</v>
       </c>
+      <c r="K23" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M23" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="P23" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="S23" t="n">
+        <v>419.07</v>
+      </c>
+      <c r="T23" t="n">
+        <v>393.89</v>
+      </c>
+      <c r="U23" t="n">
+        <v>24</v>
+      </c>
+      <c r="V23" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1399,6 +2239,42 @@
       <c r="J24" t="n">
         <v>1.037</v>
       </c>
+      <c r="K24" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M24" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="P24" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="S24" t="n">
+        <v>399.18</v>
+      </c>
+      <c r="T24" t="n">
+        <v>444.06</v>
+      </c>
+      <c r="U24" t="n">
+        <v>23</v>
+      </c>
+      <c r="V24" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1439,6 +2315,42 @@
       <c r="J25" t="n">
         <v>1.037</v>
       </c>
+      <c r="K25" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M25" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="P25" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="S25" t="n">
+        <v>370.83</v>
+      </c>
+      <c r="T25" t="n">
+        <v>367.72</v>
+      </c>
+      <c r="U25" t="n">
+        <v>17</v>
+      </c>
+      <c r="V25" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1479,6 +2391,42 @@
       <c r="J26" t="n">
         <v>1.037</v>
       </c>
+      <c r="K26" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M26" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="P26" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="S26" t="n">
+        <v>306.08</v>
+      </c>
+      <c r="T26" t="n">
+        <v>334.02</v>
+      </c>
+      <c r="U26" t="n">
+        <v>18</v>
+      </c>
+      <c r="V26" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1519,6 +2467,42 @@
       <c r="J27" t="n">
         <v>1.037</v>
       </c>
+      <c r="K27" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M27" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P27" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="S27" t="n">
+        <v>433.63</v>
+      </c>
+      <c r="T27" t="n">
+        <v>327.91</v>
+      </c>
+      <c r="U27" t="n">
+        <v>26</v>
+      </c>
+      <c r="V27" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1559,6 +2543,42 @@
       <c r="J28" t="n">
         <v>1.037</v>
       </c>
+      <c r="K28" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M28" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="P28" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S28" t="n">
+        <v>365.36</v>
+      </c>
+      <c r="T28" t="n">
+        <v>454.24</v>
+      </c>
+      <c r="U28" t="n">
+        <v>33</v>
+      </c>
+      <c r="V28" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1599,6 +2619,42 @@
       <c r="J29" t="n">
         <v>1.037</v>
       </c>
+      <c r="K29" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M29" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="P29" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="S29" t="n">
+        <v>406.23</v>
+      </c>
+      <c r="T29" t="n">
+        <v>411.89</v>
+      </c>
+      <c r="U29" t="n">
+        <v>23</v>
+      </c>
+      <c r="V29" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1639,6 +2695,42 @@
       <c r="J30" t="n">
         <v>1.037</v>
       </c>
+      <c r="K30" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M30" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="P30" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="n">
+        <v>375.65</v>
+      </c>
+      <c r="T30" t="n">
+        <v>382.81</v>
+      </c>
+      <c r="U30" t="n">
+        <v>17</v>
+      </c>
+      <c r="V30" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1679,6 +2771,42 @@
       <c r="J31" t="n">
         <v>1.037</v>
       </c>
+      <c r="K31" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M31" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-5.04</v>
+      </c>
+      <c r="P31" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="S31" t="n">
+        <v>281.51</v>
+      </c>
+      <c r="T31" t="n">
+        <v>457.8</v>
+      </c>
+      <c r="U31" t="n">
+        <v>16</v>
+      </c>
+      <c r="V31" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1719,6 +2847,42 @@
       <c r="J32" t="n">
         <v>1.017</v>
       </c>
+      <c r="K32" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M32" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="P32" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="S32" t="n">
+        <v>252.16</v>
+      </c>
+      <c r="T32" t="n">
+        <v>191.11</v>
+      </c>
+      <c r="U32" t="n">
+        <v>15</v>
+      </c>
+      <c r="V32" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1759,6 +2923,42 @@
       <c r="J33" t="n">
         <v>1.017</v>
       </c>
+      <c r="K33" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M33" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="P33" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="S33" t="n">
+        <v>225.51</v>
+      </c>
+      <c r="T33" t="n">
+        <v>251.69</v>
+      </c>
+      <c r="U33" t="n">
+        <v>17</v>
+      </c>
+      <c r="V33" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1799,6 +2999,42 @@
       <c r="J34" t="n">
         <v>1.017</v>
       </c>
+      <c r="K34" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M34" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="P34" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="S34" t="n">
+        <v>240.62</v>
+      </c>
+      <c r="T34" t="n">
+        <v>281.26</v>
+      </c>
+      <c r="U34" t="n">
+        <v>14</v>
+      </c>
+      <c r="V34" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1839,6 +3075,42 @@
       <c r="J35" t="n">
         <v>1.017</v>
       </c>
+      <c r="K35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M35" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="P35" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="S35" t="n">
+        <v>257.34</v>
+      </c>
+      <c r="T35" t="n">
+        <v>240.27</v>
+      </c>
+      <c r="U35" t="n">
+        <v>12</v>
+      </c>
+      <c r="V35" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1879,6 +3151,42 @@
       <c r="J36" t="n">
         <v>1.017</v>
       </c>
+      <c r="K36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M36" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="P36" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="S36" t="n">
+        <v>280.44</v>
+      </c>
+      <c r="T36" t="n">
+        <v>334.85</v>
+      </c>
+      <c r="U36" t="n">
+        <v>12</v>
+      </c>
+      <c r="V36" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1919,6 +3227,42 @@
       <c r="J37" t="n">
         <v>1.017</v>
       </c>
+      <c r="K37" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M37" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P37" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="S37" t="n">
+        <v>310.59</v>
+      </c>
+      <c r="T37" t="n">
+        <v>239.4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>19</v>
+      </c>
+      <c r="V37" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1959,6 +3303,42 @@
       <c r="J38" t="n">
         <v>1.017</v>
       </c>
+      <c r="K38" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M38" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="P38" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="S38" t="n">
+        <v>247.17</v>
+      </c>
+      <c r="T38" t="n">
+        <v>256.4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>15</v>
+      </c>
+      <c r="V38" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1999,6 +3379,42 @@
       <c r="J39" t="n">
         <v>1.017</v>
       </c>
+      <c r="K39" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M39" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="P39" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="S39" t="n">
+        <v>197.39</v>
+      </c>
+      <c r="T39" t="n">
+        <v>236.84</v>
+      </c>
+      <c r="U39" t="n">
+        <v>17</v>
+      </c>
+      <c r="V39" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2039,6 +3455,42 @@
       <c r="J40" t="n">
         <v>1.017</v>
       </c>
+      <c r="K40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M40" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P40" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="S40" t="n">
+        <v>280.82</v>
+      </c>
+      <c r="T40" t="n">
+        <v>234.43</v>
+      </c>
+      <c r="U40" t="n">
+        <v>12</v>
+      </c>
+      <c r="V40" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2079,6 +3531,42 @@
       <c r="J41" t="n">
         <v>1.017</v>
       </c>
+      <c r="K41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M41" t="n">
+        <v>75</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O41" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="P41" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="S41" t="n">
+        <v>263.14</v>
+      </c>
+      <c r="T41" t="n">
+        <v>303.78</v>
+      </c>
+      <c r="U41" t="n">
+        <v>12</v>
+      </c>
+      <c r="V41" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2119,6 +3607,42 @@
       <c r="J42" t="n">
         <v>1.102</v>
       </c>
+      <c r="K42" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M42" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="O42" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="P42" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="S42" t="n">
+        <v>442.29</v>
+      </c>
+      <c r="T42" t="n">
+        <v>240.1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>21</v>
+      </c>
+      <c r="V42" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2159,6 +3683,42 @@
       <c r="J43" t="n">
         <v>1.102</v>
       </c>
+      <c r="K43" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M43" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="O43" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="P43" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="S43" t="n">
+        <v>301.92</v>
+      </c>
+      <c r="T43" t="n">
+        <v>189.67</v>
+      </c>
+      <c r="U43" t="n">
+        <v>20</v>
+      </c>
+      <c r="V43" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2199,6 +3759,42 @@
       <c r="J44" t="n">
         <v>1.102</v>
       </c>
+      <c r="K44" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M44" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P44" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="S44" t="n">
+        <v>280.32</v>
+      </c>
+      <c r="T44" t="n">
+        <v>273.43</v>
+      </c>
+      <c r="U44" t="n">
+        <v>18</v>
+      </c>
+      <c r="V44" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2239,6 +3835,42 @@
       <c r="J45" t="n">
         <v>1.102</v>
       </c>
+      <c r="K45" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M45" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="P45" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="S45" t="n">
+        <v>299.04</v>
+      </c>
+      <c r="T45" t="n">
+        <v>285</v>
+      </c>
+      <c r="U45" t="n">
+        <v>15</v>
+      </c>
+      <c r="V45" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2279,6 +3911,42 @@
       <c r="J46" t="n">
         <v>1.102</v>
       </c>
+      <c r="K46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="M46" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>-7.99</v>
+      </c>
+      <c r="P46" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="S46" t="n">
+        <v>167.32</v>
+      </c>
+      <c r="T46" t="n">
+        <v>350.97</v>
+      </c>
+      <c r="U46" t="n">
+        <v>7</v>
+      </c>
+      <c r="V46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2319,6 +3987,42 @@
       <c r="J47" t="n">
         <v>1.102</v>
       </c>
+      <c r="K47" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M47" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="P47" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S47" t="n">
+        <v>369.13</v>
+      </c>
+      <c r="T47" t="n">
+        <v>319.16</v>
+      </c>
+      <c r="U47" t="n">
+        <v>27</v>
+      </c>
+      <c r="V47" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2359,6 +4063,42 @@
       <c r="J48" t="n">
         <v>1.102</v>
       </c>
+      <c r="K48" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M48" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="P48" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S48" t="n">
+        <v>327.22</v>
+      </c>
+      <c r="T48" t="n">
+        <v>318.72</v>
+      </c>
+      <c r="U48" t="n">
+        <v>22</v>
+      </c>
+      <c r="V48" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2399,6 +4139,42 @@
       <c r="J49" t="n">
         <v>1.102</v>
       </c>
+      <c r="K49" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M49" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O49" t="n">
+        <v>-5.01</v>
+      </c>
+      <c r="P49" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1</v>
+      </c>
+      <c r="S49" t="n">
+        <v>190.74</v>
+      </c>
+      <c r="T49" t="n">
+        <v>305.99</v>
+      </c>
+      <c r="U49" t="n">
+        <v>15</v>
+      </c>
+      <c r="V49" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2439,6 +4215,42 @@
       <c r="J50" t="n">
         <v>1.102</v>
       </c>
+      <c r="K50" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M50" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="O50" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="P50" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S50" t="n">
+        <v>221.99</v>
+      </c>
+      <c r="T50" t="n">
+        <v>267.32</v>
+      </c>
+      <c r="U50" t="n">
+        <v>12</v>
+      </c>
+      <c r="V50" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2479,6 +4291,42 @@
       <c r="J51" t="n">
         <v>1.102</v>
       </c>
+      <c r="K51" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M51" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="O51" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="P51" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S51" t="n">
+        <v>230.09</v>
+      </c>
+      <c r="T51" t="n">
+        <v>279.69</v>
+      </c>
+      <c r="U51" t="n">
+        <v>10</v>
+      </c>
+      <c r="V51" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2519,6 +4367,42 @@
       <c r="J52" t="n">
         <v>1.055</v>
       </c>
+      <c r="K52" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M52" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O52" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="P52" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="S52" t="n">
+        <v>405.9</v>
+      </c>
+      <c r="T52" t="n">
+        <v>220.54</v>
+      </c>
+      <c r="U52" t="n">
+        <v>24</v>
+      </c>
+      <c r="V52" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2559,6 +4443,42 @@
       <c r="J53" t="n">
         <v>1.055</v>
       </c>
+      <c r="K53" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M53" t="n">
+        <v>75</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P53" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="S53" t="n">
+        <v>257.49</v>
+      </c>
+      <c r="T53" t="n">
+        <v>230.2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>22</v>
+      </c>
+      <c r="V53" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2599,6 +4519,42 @@
       <c r="J54" t="n">
         <v>1.055</v>
       </c>
+      <c r="K54" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M54" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="O54" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="P54" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="S54" t="n">
+        <v>151.55</v>
+      </c>
+      <c r="T54" t="n">
+        <v>164.3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>14</v>
+      </c>
+      <c r="V54" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2639,6 +4595,42 @@
       <c r="J55" t="n">
         <v>1.055</v>
       </c>
+      <c r="K55" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M55" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O55" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="P55" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="S55" t="n">
+        <v>181.93</v>
+      </c>
+      <c r="T55" t="n">
+        <v>199.44</v>
+      </c>
+      <c r="U55" t="n">
+        <v>11</v>
+      </c>
+      <c r="V55" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2679,6 +4671,42 @@
       <c r="J56" t="n">
         <v>1.055</v>
       </c>
+      <c r="K56" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M56" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="O56" t="n">
+        <v>-4.88</v>
+      </c>
+      <c r="P56" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="S56" t="n">
+        <v>108.38</v>
+      </c>
+      <c r="T56" t="n">
+        <v>225.59</v>
+      </c>
+      <c r="U56" t="n">
+        <v>13</v>
+      </c>
+      <c r="V56" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2719,6 +4747,42 @@
       <c r="J57" t="n">
         <v>1.055</v>
       </c>
+      <c r="K57" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M57" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P57" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.455</v>
+      </c>
+      <c r="S57" t="n">
+        <v>300.82</v>
+      </c>
+      <c r="T57" t="n">
+        <v>260.54</v>
+      </c>
+      <c r="U57" t="n">
+        <v>22</v>
+      </c>
+      <c r="V57" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2759,6 +4823,42 @@
       <c r="J58" t="n">
         <v>1.055</v>
       </c>
+      <c r="K58" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M58" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O58" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="P58" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="S58" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="T58" t="n">
+        <v>183.69</v>
+      </c>
+      <c r="U58" t="n">
+        <v>17</v>
+      </c>
+      <c r="V58" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2799,6 +4899,42 @@
       <c r="J59" t="n">
         <v>1.055</v>
       </c>
+      <c r="K59" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M59" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="O59" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P59" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
+      <c r="S59" t="n">
+        <v>209.08</v>
+      </c>
+      <c r="T59" t="n">
+        <v>160.64</v>
+      </c>
+      <c r="U59" t="n">
+        <v>12</v>
+      </c>
+      <c r="V59" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2839,6 +4975,42 @@
       <c r="J60" t="n">
         <v>1.055</v>
       </c>
+      <c r="K60" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M60" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="P60" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="S60" t="n">
+        <v>208.03</v>
+      </c>
+      <c r="T60" t="n">
+        <v>258.9</v>
+      </c>
+      <c r="U60" t="n">
+        <v>11</v>
+      </c>
+      <c r="V60" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2879,6 +5051,42 @@
       <c r="J61" t="n">
         <v>1.055</v>
       </c>
+      <c r="K61" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M61" t="n">
+        <v>50</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O61" t="n">
+        <v>-4.28</v>
+      </c>
+      <c r="P61" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="S61" t="n">
+        <v>138.92</v>
+      </c>
+      <c r="T61" t="n">
+        <v>241.55</v>
+      </c>
+      <c r="U61" t="n">
+        <v>9</v>
+      </c>
+      <c r="V61" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2917,7 +5125,43 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>0.9950000000000001</v>
+        <v>0.9949999999999999</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M62" t="n">
+        <v>81</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O62" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="P62" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="S62" t="n">
+        <v>171.86</v>
+      </c>
+      <c r="T62" t="n">
+        <v>102.41</v>
+      </c>
+      <c r="U62" t="n">
+        <v>13</v>
+      </c>
+      <c r="V62" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="63">
@@ -2957,7 +5201,43 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>0.9950000000000001</v>
+        <v>0.9949999999999999</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M63" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O63" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P63" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="S63" t="n">
+        <v>237.65</v>
+      </c>
+      <c r="T63" t="n">
+        <v>163.27</v>
+      </c>
+      <c r="U63" t="n">
+        <v>16</v>
+      </c>
+      <c r="V63" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="64">
@@ -2997,7 +5277,43 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>0.9950000000000001</v>
+        <v>0.9949999999999999</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M64" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P64" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="n">
+        <v>202.99</v>
+      </c>
+      <c r="T64" t="n">
+        <v>192.59</v>
+      </c>
+      <c r="U64" t="n">
+        <v>14</v>
+      </c>
+      <c r="V64" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="65">
@@ -3037,7 +5353,43 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>0.9950000000000001</v>
+        <v>0.9949999999999999</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M65" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="N65" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="O65" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="P65" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1</v>
+      </c>
+      <c r="S65" t="n">
+        <v>183.45</v>
+      </c>
+      <c r="T65" t="n">
+        <v>130.85</v>
+      </c>
+      <c r="U65" t="n">
+        <v>16</v>
+      </c>
+      <c r="V65" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="66">
@@ -3077,7 +5429,43 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>0.9950000000000001</v>
+        <v>0.9949999999999999</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M66" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P66" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1</v>
+      </c>
+      <c r="S66" t="n">
+        <v>143.76</v>
+      </c>
+      <c r="T66" t="n">
+        <v>141.96</v>
+      </c>
+      <c r="U66" t="n">
+        <v>14</v>
+      </c>
+      <c r="V66" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="67">
@@ -3117,7 +5505,43 @@
         <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>0.9950000000000001</v>
+        <v>0.9949999999999999</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M67" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P67" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S67" t="n">
+        <v>180.63</v>
+      </c>
+      <c r="T67" t="n">
+        <v>139.47</v>
+      </c>
+      <c r="U67" t="n">
+        <v>12</v>
+      </c>
+      <c r="V67" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="68">
@@ -3157,7 +5581,43 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>0.9950000000000001</v>
+        <v>0.9949999999999999</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M68" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="O68" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="P68" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="S68" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="T68" t="n">
+        <v>225.15</v>
+      </c>
+      <c r="U68" t="n">
+        <v>14</v>
+      </c>
+      <c r="V68" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="69">
@@ -3197,7 +5657,43 @@
         <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>0.9950000000000001</v>
+        <v>0.9949999999999999</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M69" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="O69" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="P69" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S69" t="n">
+        <v>125.21</v>
+      </c>
+      <c r="T69" t="n">
+        <v>168.68</v>
+      </c>
+      <c r="U69" t="n">
+        <v>9</v>
+      </c>
+      <c r="V69" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="70">
@@ -3237,7 +5733,43 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>0.9950000000000001</v>
+        <v>0.9949999999999999</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M70" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>-3.96</v>
+      </c>
+      <c r="P70" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S70" t="n">
+        <v>103.39</v>
+      </c>
+      <c r="T70" t="n">
+        <v>186.46</v>
+      </c>
+      <c r="U70" t="n">
+        <v>7</v>
+      </c>
+      <c r="V70" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -3277,7 +5809,43 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>0.9950000000000001</v>
+        <v>0.9949999999999999</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M71" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="O71" t="n">
+        <v>-4.63</v>
+      </c>
+      <c r="P71" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S71" t="n">
+        <v>122.79</v>
+      </c>
+      <c r="T71" t="n">
+        <v>219.99</v>
+      </c>
+      <c r="U71" t="n">
+        <v>8</v>
+      </c>
+      <c r="V71" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -3319,6 +5887,42 @@
       <c r="J72" t="n">
         <v>1.045</v>
       </c>
+      <c r="K72" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M72" t="n">
+        <v>80</v>
+      </c>
+      <c r="N72" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O72" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="P72" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S72" t="n">
+        <v>311.53</v>
+      </c>
+      <c r="T72" t="n">
+        <v>211.28</v>
+      </c>
+      <c r="U72" t="n">
+        <v>18</v>
+      </c>
+      <c r="V72" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3359,6 +5963,42 @@
       <c r="J73" t="n">
         <v>1.045</v>
       </c>
+      <c r="K73" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M73" t="n">
+        <v>90</v>
+      </c>
+      <c r="N73" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P73" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1.385</v>
+      </c>
+      <c r="S73" t="n">
+        <v>228.43</v>
+      </c>
+      <c r="T73" t="n">
+        <v>208.11</v>
+      </c>
+      <c r="U73" t="n">
+        <v>22</v>
+      </c>
+      <c r="V73" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3399,6 +6039,42 @@
       <c r="J74" t="n">
         <v>1.045</v>
       </c>
+      <c r="K74" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M74" t="n">
+        <v>65</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P74" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="S74" t="n">
+        <v>218.37</v>
+      </c>
+      <c r="T74" t="n">
+        <v>183.86</v>
+      </c>
+      <c r="U74" t="n">
+        <v>18</v>
+      </c>
+      <c r="V74" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3439,6 +6115,42 @@
       <c r="J75" t="n">
         <v>1.045</v>
       </c>
+      <c r="K75" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M75" t="n">
+        <v>70</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="P75" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="S75" t="n">
+        <v>194.28</v>
+      </c>
+      <c r="T75" t="n">
+        <v>190.9</v>
+      </c>
+      <c r="U75" t="n">
+        <v>13</v>
+      </c>
+      <c r="V75" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3479,6 +6191,42 @@
       <c r="J76" t="n">
         <v>1.045</v>
       </c>
+      <c r="K76" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M76" t="n">
+        <v>75</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="O76" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="P76" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="S76" t="n">
+        <v>160.31</v>
+      </c>
+      <c r="T76" t="n">
+        <v>204.12</v>
+      </c>
+      <c r="U76" t="n">
+        <v>11</v>
+      </c>
+      <c r="V76" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3511,7 +6259,7 @@
         <v>1.49</v>
       </c>
       <c r="H77" t="n">
-        <v>0.9040000000000001</v>
+        <v>0.9039999999999999</v>
       </c>
       <c r="I77" t="n">
         <v>20</v>
@@ -3519,6 +6267,42 @@
       <c r="J77" t="n">
         <v>1.045</v>
       </c>
+      <c r="K77" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M77" t="n">
+        <v>65</v>
+      </c>
+      <c r="N77" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O77" t="n">
+        <v>6</v>
+      </c>
+      <c r="P77" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R77" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="S77" t="n">
+        <v>313.48</v>
+      </c>
+      <c r="T77" t="n">
+        <v>193.57</v>
+      </c>
+      <c r="U77" t="n">
+        <v>14</v>
+      </c>
+      <c r="V77" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3551,7 +6335,7 @@
         <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>0.9040000000000001</v>
+        <v>0.9039999999999999</v>
       </c>
       <c r="I78" t="n">
         <v>20</v>
@@ -3559,6 +6343,42 @@
       <c r="J78" t="n">
         <v>1.045</v>
       </c>
+      <c r="K78" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M78" t="n">
+        <v>45</v>
+      </c>
+      <c r="N78" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O78" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="P78" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="S78" t="n">
+        <v>224.97</v>
+      </c>
+      <c r="T78" t="n">
+        <v>238.43</v>
+      </c>
+      <c r="U78" t="n">
+        <v>13</v>
+      </c>
+      <c r="V78" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3591,7 +6411,7 @@
         <v>0.7</v>
       </c>
       <c r="H79" t="n">
-        <v>0.9040000000000001</v>
+        <v>0.9039999999999999</v>
       </c>
       <c r="I79" t="n">
         <v>20</v>
@@ -3599,6 +6419,42 @@
       <c r="J79" t="n">
         <v>1.045</v>
       </c>
+      <c r="K79" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M79" t="n">
+        <v>45</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="O79" t="n">
+        <v>-3.32</v>
+      </c>
+      <c r="P79" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="S79" t="n">
+        <v>156.87</v>
+      </c>
+      <c r="T79" t="n">
+        <v>223.33</v>
+      </c>
+      <c r="U79" t="n">
+        <v>9</v>
+      </c>
+      <c r="V79" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3631,7 +6487,7 @@
         <v>0.7</v>
       </c>
       <c r="H80" t="n">
-        <v>0.9040000000000001</v>
+        <v>0.9039999999999999</v>
       </c>
       <c r="I80" t="n">
         <v>20</v>
@@ -3639,6 +6495,42 @@
       <c r="J80" t="n">
         <v>1.045</v>
       </c>
+      <c r="K80" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M80" t="n">
+        <v>45</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O80" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="P80" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="S80" t="n">
+        <v>150.95</v>
+      </c>
+      <c r="T80" t="n">
+        <v>201.76</v>
+      </c>
+      <c r="U80" t="n">
+        <v>9</v>
+      </c>
+      <c r="V80" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3671,7 +6563,7 @@
         <v>0.63</v>
       </c>
       <c r="H81" t="n">
-        <v>0.9040000000000001</v>
+        <v>0.9039999999999999</v>
       </c>
       <c r="I81" t="n">
         <v>20</v>
@@ -3679,6 +6571,42 @@
       <c r="J81" t="n">
         <v>1.045</v>
       </c>
+      <c r="K81" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M81" t="n">
+        <v>50</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="O81" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="P81" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="S81" t="n">
+        <v>151.91</v>
+      </c>
+      <c r="T81" t="n">
+        <v>255.88</v>
+      </c>
+      <c r="U81" t="n">
+        <v>9</v>
+      </c>
+      <c r="V81" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3719,6 +6647,42 @@
       <c r="J82" t="n">
         <v>1.086</v>
       </c>
+      <c r="K82" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M82" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O82" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P82" t="n">
+        <v>148.1</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="R82" t="n">
+        <v>1.692</v>
+      </c>
+      <c r="S82" t="n">
+        <v>245.61</v>
+      </c>
+      <c r="T82" t="n">
+        <v>67.88</v>
+      </c>
+      <c r="U82" t="n">
+        <v>22</v>
+      </c>
+      <c r="V82" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3759,6 +6723,42 @@
       <c r="J83" t="n">
         <v>1.086</v>
       </c>
+      <c r="K83" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M83" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="N83" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O83" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="P83" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="S83" t="n">
+        <v>190.17</v>
+      </c>
+      <c r="T83" t="n">
+        <v>120.68</v>
+      </c>
+      <c r="U83" t="n">
+        <v>14</v>
+      </c>
+      <c r="V83" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3799,6 +6799,42 @@
       <c r="J84" t="n">
         <v>1.086</v>
       </c>
+      <c r="K84" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M84" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="O84" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P84" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="S84" t="n">
+        <v>123.15</v>
+      </c>
+      <c r="T84" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="U84" t="n">
+        <v>8</v>
+      </c>
+      <c r="V84" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3839,6 +6875,42 @@
       <c r="J85" t="n">
         <v>1.086</v>
       </c>
+      <c r="K85" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M85" t="n">
+        <v>75</v>
+      </c>
+      <c r="N85" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O85" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="P85" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="S85" t="n">
+        <v>170.73</v>
+      </c>
+      <c r="T85" t="n">
+        <v>133.79</v>
+      </c>
+      <c r="U85" t="n">
+        <v>13</v>
+      </c>
+      <c r="V85" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3879,6 +6951,42 @@
       <c r="J86" t="n">
         <v>1.086</v>
       </c>
+      <c r="K86" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M86" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="O86" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="P86" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="S86" t="n">
+        <v>94.94</v>
+      </c>
+      <c r="T86" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="U86" t="n">
+        <v>12</v>
+      </c>
+      <c r="V86" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3911,7 +7019,7 @@
         <v>0.91</v>
       </c>
       <c r="H87" t="n">
-        <v>0.66</v>
+        <v>0.6599999999999999</v>
       </c>
       <c r="I87" t="n">
         <v>16</v>
@@ -3919,6 +7027,42 @@
       <c r="J87" t="n">
         <v>1.086</v>
       </c>
+      <c r="K87" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M87" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O87" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="P87" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="R87" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="S87" t="n">
+        <v>126.05</v>
+      </c>
+      <c r="T87" t="n">
+        <v>145.37</v>
+      </c>
+      <c r="U87" t="n">
+        <v>8</v>
+      </c>
+      <c r="V87" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3951,7 +7095,7 @@
         <v>0.84</v>
       </c>
       <c r="H88" t="n">
-        <v>0.66</v>
+        <v>0.6599999999999999</v>
       </c>
       <c r="I88" t="n">
         <v>16</v>
@@ -3959,6 +7103,42 @@
       <c r="J88" t="n">
         <v>1.086</v>
       </c>
+      <c r="K88" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M88" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="O88" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="P88" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="S88" t="n">
+        <v>94.93000000000001</v>
+      </c>
+      <c r="T88" t="n">
+        <v>166.39</v>
+      </c>
+      <c r="U88" t="n">
+        <v>8</v>
+      </c>
+      <c r="V88" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3991,7 +7171,7 @@
         <v>0.66</v>
       </c>
       <c r="H89" t="n">
-        <v>0.66</v>
+        <v>0.6599999999999999</v>
       </c>
       <c r="I89" t="n">
         <v>16</v>
@@ -3999,6 +7179,42 @@
       <c r="J89" t="n">
         <v>1.086</v>
       </c>
+      <c r="K89" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M89" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="O89" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="P89" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="R89" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="S89" t="n">
+        <v>110.47</v>
+      </c>
+      <c r="T89" t="n">
+        <v>152.92</v>
+      </c>
+      <c r="U89" t="n">
+        <v>9</v>
+      </c>
+      <c r="V89" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4031,7 +7247,7 @@
         <v>0.46</v>
       </c>
       <c r="H90" t="n">
-        <v>0.66</v>
+        <v>0.6599999999999999</v>
       </c>
       <c r="I90" t="n">
         <v>16</v>
@@ -4039,6 +7255,42 @@
       <c r="J90" t="n">
         <v>1.086</v>
       </c>
+      <c r="K90" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M90" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>-4.52</v>
+      </c>
+      <c r="P90" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="S90" t="n">
+        <v>76.04000000000001</v>
+      </c>
+      <c r="T90" t="n">
+        <v>148.42</v>
+      </c>
+      <c r="U90" t="n">
+        <v>3</v>
+      </c>
+      <c r="V90" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4071,7 +7323,7 @@
         <v>0.43</v>
       </c>
       <c r="H91" t="n">
-        <v>0.66</v>
+        <v>0.6599999999999999</v>
       </c>
       <c r="I91" t="n">
         <v>16</v>
@@ -4079,6 +7331,42 @@
       <c r="J91" t="n">
         <v>1.086</v>
       </c>
+      <c r="K91" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M91" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O91" t="n">
+        <v>-8.09</v>
+      </c>
+      <c r="P91" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="S91" t="n">
+        <v>82.03</v>
+      </c>
+      <c r="T91" t="n">
+        <v>211.49</v>
+      </c>
+      <c r="U91" t="n">
+        <v>5</v>
+      </c>
+      <c r="V91" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4119,6 +7407,42 @@
       <c r="J92" t="n">
         <v>1.121</v>
       </c>
+      <c r="K92" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M92" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="N92" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O92" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="P92" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R92" t="n">
+        <v>1.385</v>
+      </c>
+      <c r="S92" t="n">
+        <v>311.78</v>
+      </c>
+      <c r="T92" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="U92" t="n">
+        <v>22</v>
+      </c>
+      <c r="V92" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4159,6 +7483,42 @@
       <c r="J93" t="n">
         <v>1.121</v>
       </c>
+      <c r="K93" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M93" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="N93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O93" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="P93" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="R93" t="n">
+        <v>1</v>
+      </c>
+      <c r="S93" t="n">
+        <v>264.42</v>
+      </c>
+      <c r="T93" t="n">
+        <v>65.09</v>
+      </c>
+      <c r="U93" t="n">
+        <v>15</v>
+      </c>
+      <c r="V93" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4199,6 +7559,42 @@
       <c r="J94" t="n">
         <v>1.121</v>
       </c>
+      <c r="K94" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M94" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="N94" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O94" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P94" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R94" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="S94" t="n">
+        <v>156.78</v>
+      </c>
+      <c r="T94" t="n">
+        <v>140.68</v>
+      </c>
+      <c r="U94" t="n">
+        <v>14</v>
+      </c>
+      <c r="V94" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4239,6 +7635,42 @@
       <c r="J95" t="n">
         <v>1.121</v>
       </c>
+      <c r="K95" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M95" t="n">
+        <v>75</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="O95" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="P95" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="S95" t="n">
+        <v>177.16</v>
+      </c>
+      <c r="T95" t="n">
+        <v>130.04</v>
+      </c>
+      <c r="U95" t="n">
+        <v>8</v>
+      </c>
+      <c r="V95" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4279,6 +7711,42 @@
       <c r="J96" t="n">
         <v>1.121</v>
       </c>
+      <c r="K96" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M96" t="n">
+        <v>75</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="O96" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="P96" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="S96" t="n">
+        <v>130.1</v>
+      </c>
+      <c r="T96" t="n">
+        <v>140.78</v>
+      </c>
+      <c r="U96" t="n">
+        <v>6</v>
+      </c>
+      <c r="V96" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4319,6 +7787,42 @@
       <c r="J97" t="n">
         <v>1.121</v>
       </c>
+      <c r="K97" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M97" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="N97" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="P97" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R97" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="S97" t="n">
+        <v>157.77</v>
+      </c>
+      <c r="T97" t="n">
+        <v>154.32</v>
+      </c>
+      <c r="U97" t="n">
+        <v>14</v>
+      </c>
+      <c r="V97" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4359,6 +7863,42 @@
       <c r="J98" t="n">
         <v>1.121</v>
       </c>
+      <c r="K98" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M98" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N98" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="O98" t="n">
+        <v>-8.02</v>
+      </c>
+      <c r="P98" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="R98" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="S98" t="n">
+        <v>136.39</v>
+      </c>
+      <c r="T98" t="n">
+        <v>264.75</v>
+      </c>
+      <c r="U98" t="n">
+        <v>11</v>
+      </c>
+      <c r="V98" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4399,6 +7939,42 @@
       <c r="J99" t="n">
         <v>1.121</v>
       </c>
+      <c r="K99" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M99" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="O99" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="P99" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="S99" t="n">
+        <v>125.98</v>
+      </c>
+      <c r="T99" t="n">
+        <v>191.59</v>
+      </c>
+      <c r="U99" t="n">
+        <v>5</v>
+      </c>
+      <c r="V99" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4439,6 +8015,42 @@
       <c r="J100" t="n">
         <v>1.121</v>
       </c>
+      <c r="K100" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M100" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="P100" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="n">
+        <v>74.41</v>
+      </c>
+      <c r="T100" t="n">
+        <v>197.65</v>
+      </c>
+      <c r="U100" t="n">
+        <v>3</v>
+      </c>
+      <c r="V100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4479,6 +8091,42 @@
       <c r="J101" t="n">
         <v>1.121</v>
       </c>
+      <c r="K101" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M101" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="O101" t="n">
+        <v>-9.130000000000001</v>
+      </c>
+      <c r="P101" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="S101" t="n">
+        <v>85.92</v>
+      </c>
+      <c r="T101" t="n">
+        <v>231.9</v>
+      </c>
+      <c r="U101" t="n">
+        <v>3</v>
+      </c>
+      <c r="V101" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4519,6 +8167,42 @@
       <c r="J102" t="n">
         <v>1.109</v>
       </c>
+      <c r="K102" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M102" t="n">
+        <v>81</v>
+      </c>
+      <c r="N102" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="O102" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P102" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R102" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="S102" t="n">
+        <v>302.79</v>
+      </c>
+      <c r="T102" t="n">
+        <v>246.2</v>
+      </c>
+      <c r="U102" t="n">
+        <v>19</v>
+      </c>
+      <c r="V102" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4559,6 +8243,42 @@
       <c r="J103" t="n">
         <v>1.109</v>
       </c>
+      <c r="K103" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M103" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="O103" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="P103" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="S103" t="n">
+        <v>289.55</v>
+      </c>
+      <c r="T103" t="n">
+        <v>194.21</v>
+      </c>
+      <c r="U103" t="n">
+        <v>16</v>
+      </c>
+      <c r="V103" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4599,6 +8319,42 @@
       <c r="J104" t="n">
         <v>1.109</v>
       </c>
+      <c r="K104" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M104" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="N104" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="O104" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="P104" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="S104" t="n">
+        <v>244.96</v>
+      </c>
+      <c r="T104" t="n">
+        <v>150.67</v>
+      </c>
+      <c r="U104" t="n">
+        <v>10</v>
+      </c>
+      <c r="V104" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4639,6 +8395,42 @@
       <c r="J105" t="n">
         <v>1.109</v>
       </c>
+      <c r="K105" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M105" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="N105" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O105" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P105" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="S105" t="n">
+        <v>259.78</v>
+      </c>
+      <c r="T105" t="n">
+        <v>224.35</v>
+      </c>
+      <c r="U105" t="n">
+        <v>14</v>
+      </c>
+      <c r="V105" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4679,6 +8471,42 @@
       <c r="J106" t="n">
         <v>1.109</v>
       </c>
+      <c r="K106" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M106" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="N106" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="O106" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="P106" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="R106" t="n">
+        <v>1</v>
+      </c>
+      <c r="S106" t="n">
+        <v>245.62</v>
+      </c>
+      <c r="T106" t="n">
+        <v>264.34</v>
+      </c>
+      <c r="U106" t="n">
+        <v>15</v>
+      </c>
+      <c r="V106" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4719,6 +8547,42 @@
       <c r="J107" t="n">
         <v>1.109</v>
       </c>
+      <c r="K107" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M107" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="N107" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O107" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="P107" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R107" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="S107" t="n">
+        <v>343.61</v>
+      </c>
+      <c r="T107" t="n">
+        <v>215.91</v>
+      </c>
+      <c r="U107" t="n">
+        <v>23</v>
+      </c>
+      <c r="V107" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4759,6 +8623,42 @@
       <c r="J108" t="n">
         <v>1.109</v>
       </c>
+      <c r="K108" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M108" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="O108" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="P108" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S108" t="n">
+        <v>219.02</v>
+      </c>
+      <c r="T108" t="n">
+        <v>181.53</v>
+      </c>
+      <c r="U108" t="n">
+        <v>15</v>
+      </c>
+      <c r="V108" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4799,6 +8699,42 @@
       <c r="J109" t="n">
         <v>1.109</v>
       </c>
+      <c r="K109" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M109" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="O109" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="P109" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S109" t="n">
+        <v>253.66</v>
+      </c>
+      <c r="T109" t="n">
+        <v>310.69</v>
+      </c>
+      <c r="U109" t="n">
+        <v>10</v>
+      </c>
+      <c r="V109" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4839,6 +8775,42 @@
       <c r="J110" t="n">
         <v>1.109</v>
       </c>
+      <c r="K110" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M110" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O110" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="P110" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S110" t="n">
+        <v>122.53</v>
+      </c>
+      <c r="T110" t="n">
+        <v>275.85</v>
+      </c>
+      <c r="U110" t="n">
+        <v>10</v>
+      </c>
+      <c r="V110" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4879,6 +8851,42 @@
       <c r="J111" t="n">
         <v>1.109</v>
       </c>
+      <c r="K111" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M111" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="O111" t="n">
+        <v>-10.37</v>
+      </c>
+      <c r="P111" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="S111" t="n">
+        <v>140.94</v>
+      </c>
+      <c r="T111" t="n">
+        <v>358.71</v>
+      </c>
+      <c r="U111" t="n">
+        <v>9</v>
+      </c>
+      <c r="V111" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4919,6 +8927,42 @@
       <c r="J112" t="n">
         <v>1.053</v>
       </c>
+      <c r="K112" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M112" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="N112" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O112" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="P112" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R112" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="S112" t="n">
+        <v>338</v>
+      </c>
+      <c r="T112" t="n">
+        <v>146.31</v>
+      </c>
+      <c r="U112" t="n">
+        <v>21</v>
+      </c>
+      <c r="V112" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4959,6 +9003,42 @@
       <c r="J113" t="n">
         <v>1.053</v>
       </c>
+      <c r="K113" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M113" t="n">
+        <v>75</v>
+      </c>
+      <c r="N113" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O113" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="P113" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R113" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="S113" t="n">
+        <v>338.56</v>
+      </c>
+      <c r="T113" t="n">
+        <v>249.95</v>
+      </c>
+      <c r="U113" t="n">
+        <v>20</v>
+      </c>
+      <c r="V113" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4999,6 +9079,42 @@
       <c r="J114" t="n">
         <v>1.053</v>
       </c>
+      <c r="K114" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M114" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="N114" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O114" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="P114" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>1</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="S114" t="n">
+        <v>233.76</v>
+      </c>
+      <c r="T114" t="n">
+        <v>285.86</v>
+      </c>
+      <c r="U114" t="n">
+        <v>17</v>
+      </c>
+      <c r="V114" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5039,6 +9155,42 @@
       <c r="J115" t="n">
         <v>1.053</v>
       </c>
+      <c r="K115" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M115" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="O115" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="P115" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>1</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="S115" t="n">
+        <v>270.11</v>
+      </c>
+      <c r="T115" t="n">
+        <v>278.14</v>
+      </c>
+      <c r="U115" t="n">
+        <v>14</v>
+      </c>
+      <c r="V115" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5079,6 +9231,42 @@
       <c r="J116" t="n">
         <v>1.053</v>
       </c>
+      <c r="K116" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M116" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>-4.13</v>
+      </c>
+      <c r="P116" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="S116" t="n">
+        <v>154.53</v>
+      </c>
+      <c r="T116" t="n">
+        <v>253.66</v>
+      </c>
+      <c r="U116" t="n">
+        <v>8</v>
+      </c>
+      <c r="V116" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5119,6 +9307,42 @@
       <c r="J117" t="n">
         <v>1.053</v>
       </c>
+      <c r="K117" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M117" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O117" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P117" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R117" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="S117" t="n">
+        <v>247.44</v>
+      </c>
+      <c r="T117" t="n">
+        <v>190.31</v>
+      </c>
+      <c r="U117" t="n">
+        <v>20</v>
+      </c>
+      <c r="V117" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5159,6 +9383,42 @@
       <c r="J118" t="n">
         <v>1.053</v>
       </c>
+      <c r="K118" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M118" t="n">
+        <v>75</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="O118" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P118" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="S118" t="n">
+        <v>266.64</v>
+      </c>
+      <c r="T118" t="n">
+        <v>240.92</v>
+      </c>
+      <c r="U118" t="n">
+        <v>14</v>
+      </c>
+      <c r="V118" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5199,6 +9459,42 @@
       <c r="J119" t="n">
         <v>1.053</v>
       </c>
+      <c r="K119" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M119" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N119" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P119" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="S119" t="n">
+        <v>288.45</v>
+      </c>
+      <c r="T119" t="n">
+        <v>286.77</v>
+      </c>
+      <c r="U119" t="n">
+        <v>16</v>
+      </c>
+      <c r="V119" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5239,6 +9535,42 @@
       <c r="J120" t="n">
         <v>1.053</v>
       </c>
+      <c r="K120" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M120" t="n">
+        <v>75</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="O120" t="n">
+        <v>-5.04</v>
+      </c>
+      <c r="P120" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="R120" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="S120" t="n">
+        <v>213.34</v>
+      </c>
+      <c r="T120" t="n">
+        <v>334.34</v>
+      </c>
+      <c r="U120" t="n">
+        <v>14</v>
+      </c>
+      <c r="V120" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5279,6 +9611,42 @@
       <c r="J121" t="n">
         <v>1.053</v>
       </c>
+      <c r="K121" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M121" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O121" t="n">
+        <v>-3.52</v>
+      </c>
+      <c r="P121" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="S121" t="n">
+        <v>198.07</v>
+      </c>
+      <c r="T121" t="n">
+        <v>282.62</v>
+      </c>
+      <c r="U121" t="n">
+        <v>10</v>
+      </c>
+      <c r="V121" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5319,6 +9687,42 @@
       <c r="J122" t="n">
         <v>1.062</v>
       </c>
+      <c r="K122" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M122" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="P122" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R122" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="S122" t="n">
+        <v>212.57</v>
+      </c>
+      <c r="T122" t="n">
+        <v>204.51</v>
+      </c>
+      <c r="U122" t="n">
+        <v>20</v>
+      </c>
+      <c r="V122" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5359,6 +9763,42 @@
       <c r="J123" t="n">
         <v>1.062</v>
       </c>
+      <c r="K123" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M123" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="N123" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O123" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P123" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="R123" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="S123" t="n">
+        <v>245.21</v>
+      </c>
+      <c r="T123" t="n">
+        <v>196.05</v>
+      </c>
+      <c r="U123" t="n">
+        <v>17</v>
+      </c>
+      <c r="V123" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5399,6 +9839,42 @@
       <c r="J124" t="n">
         <v>1.062</v>
       </c>
+      <c r="K124" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M124" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="O124" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="P124" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="S124" t="n">
+        <v>256.38</v>
+      </c>
+      <c r="T124" t="n">
+        <v>173.26</v>
+      </c>
+      <c r="U124" t="n">
+        <v>15</v>
+      </c>
+      <c r="V124" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5439,6 +9915,42 @@
       <c r="J125" t="n">
         <v>1.062</v>
       </c>
+      <c r="K125" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M125" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N125" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="O125" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="P125" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="R125" t="n">
+        <v>1</v>
+      </c>
+      <c r="S125" t="n">
+        <v>196.73</v>
+      </c>
+      <c r="T125" t="n">
+        <v>209.84</v>
+      </c>
+      <c r="U125" t="n">
+        <v>16</v>
+      </c>
+      <c r="V125" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5479,6 +9991,42 @@
       <c r="J126" t="n">
         <v>1.062</v>
       </c>
+      <c r="K126" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M126" t="n">
+        <v>75</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="O126" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="P126" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="S126" t="n">
+        <v>220.57</v>
+      </c>
+      <c r="T126" t="n">
+        <v>248.95</v>
+      </c>
+      <c r="U126" t="n">
+        <v>10</v>
+      </c>
+      <c r="V126" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5519,6 +10067,42 @@
       <c r="J127" t="n">
         <v>1.062</v>
       </c>
+      <c r="K127" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M127" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="N127" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O127" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="P127" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1.182</v>
+      </c>
+      <c r="S127" t="n">
+        <v>358.91</v>
+      </c>
+      <c r="T127" t="n">
+        <v>206.4</v>
+      </c>
+      <c r="U127" t="n">
+        <v>27</v>
+      </c>
+      <c r="V127" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5559,6 +10143,42 @@
       <c r="J128" t="n">
         <v>1.062</v>
       </c>
+      <c r="K128" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M128" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N128" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O128" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="P128" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="R128" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="S128" t="n">
+        <v>168.92</v>
+      </c>
+      <c r="T128" t="n">
+        <v>234.47</v>
+      </c>
+      <c r="U128" t="n">
+        <v>17</v>
+      </c>
+      <c r="V128" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5599,6 +10219,42 @@
       <c r="J129" t="n">
         <v>1.062</v>
       </c>
+      <c r="K129" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M129" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O129" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="P129" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="S129" t="n">
+        <v>153.68</v>
+      </c>
+      <c r="T129" t="n">
+        <v>205.47</v>
+      </c>
+      <c r="U129" t="n">
+        <v>13</v>
+      </c>
+      <c r="V129" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5639,6 +10295,42 @@
       <c r="J130" t="n">
         <v>1.062</v>
       </c>
+      <c r="K130" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M130" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="O130" t="n">
+        <v>-3.65</v>
+      </c>
+      <c r="P130" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="S130" t="n">
+        <v>170.81</v>
+      </c>
+      <c r="T130" t="n">
+        <v>258.33</v>
+      </c>
+      <c r="U130" t="n">
+        <v>11</v>
+      </c>
+      <c r="V130" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5679,6 +10371,42 @@
       <c r="J131" t="n">
         <v>1.062</v>
       </c>
+      <c r="K131" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M131" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="O131" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="P131" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>180.26</v>
+      </c>
+      <c r="T131" t="n">
+        <v>226.78</v>
+      </c>
+      <c r="U131" t="n">
+        <v>11</v>
+      </c>
+      <c r="V131" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5719,6 +10447,42 @@
       <c r="J132" t="n">
         <v>1.115</v>
       </c>
+      <c r="K132" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M132" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P132" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="R132" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="S132" t="n">
+        <v>159.09</v>
+      </c>
+      <c r="T132" t="n">
+        <v>152.04</v>
+      </c>
+      <c r="U132" t="n">
+        <v>8</v>
+      </c>
+      <c r="V132" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5759,6 +10523,42 @@
       <c r="J133" t="n">
         <v>1.115</v>
       </c>
+      <c r="K133" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M133" t="n">
+        <v>50</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="O133" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="P133" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R133" t="n">
+        <v>1</v>
+      </c>
+      <c r="S133" t="n">
+        <v>165.28</v>
+      </c>
+      <c r="T133" t="n">
+        <v>197.63</v>
+      </c>
+      <c r="U133" t="n">
+        <v>9</v>
+      </c>
+      <c r="V133" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5799,6 +10599,42 @@
       <c r="J134" t="n">
         <v>1.115</v>
       </c>
+      <c r="K134" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M134" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="O134" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="P134" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="S134" t="n">
+        <v>116.83</v>
+      </c>
+      <c r="T134" t="n">
+        <v>196.02</v>
+      </c>
+      <c r="U134" t="n">
+        <v>7</v>
+      </c>
+      <c r="V134" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5839,6 +10675,42 @@
       <c r="J135" t="n">
         <v>1.115</v>
       </c>
+      <c r="K135" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L135" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" t="n">
+        <v>50</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-8.77</v>
+      </c>
+      <c r="P135" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>97.34</v>
+      </c>
+      <c r="T135" t="n">
+        <v>237.58</v>
+      </c>
+      <c r="U135" t="n">
+        <v>6</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5879,6 +10751,42 @@
       <c r="J136" t="n">
         <v>1.115</v>
       </c>
+      <c r="K136" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L136" t="n">
+        <v>1</v>
+      </c>
+      <c r="M136" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="O136" t="n">
+        <v>-5.87</v>
+      </c>
+      <c r="P136" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R136" t="n">
+        <v>1</v>
+      </c>
+      <c r="S136" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="T136" t="n">
+        <v>221.05</v>
+      </c>
+      <c r="U136" t="n">
+        <v>6</v>
+      </c>
+      <c r="V136" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5919,6 +10827,42 @@
       <c r="J137" t="n">
         <v>1.115</v>
       </c>
+      <c r="K137" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M137" t="n">
+        <v>100</v>
+      </c>
+      <c r="N137" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O137" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="P137" t="n">
+        <v>160.2</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R137" t="n">
+        <v>1.923</v>
+      </c>
+      <c r="S137" t="n">
+        <v>335.56</v>
+      </c>
+      <c r="T137" t="n">
+        <v>137.84</v>
+      </c>
+      <c r="U137" t="n">
+        <v>28</v>
+      </c>
+      <c r="V137" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5959,6 +10903,42 @@
       <c r="J138" t="n">
         <v>1.115</v>
       </c>
+      <c r="K138" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M138" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="N138" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O138" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="P138" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R138" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="S138" t="n">
+        <v>258.08</v>
+      </c>
+      <c r="T138" t="n">
+        <v>108.53</v>
+      </c>
+      <c r="U138" t="n">
+        <v>17</v>
+      </c>
+      <c r="V138" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5999,6 +10979,42 @@
       <c r="J139" t="n">
         <v>1.115</v>
       </c>
+      <c r="K139" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M139" t="n">
+        <v>75</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="O139" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P139" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="S139" t="n">
+        <v>160.58</v>
+      </c>
+      <c r="T139" t="n">
+        <v>141.92</v>
+      </c>
+      <c r="U139" t="n">
+        <v>13</v>
+      </c>
+      <c r="V139" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6039,6 +11055,42 @@
       <c r="J140" t="n">
         <v>1.115</v>
       </c>
+      <c r="K140" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M140" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P140" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="S140" t="n">
+        <v>107.19</v>
+      </c>
+      <c r="T140" t="n">
+        <v>95.95999999999999</v>
+      </c>
+      <c r="U140" t="n">
+        <v>8</v>
+      </c>
+      <c r="V140" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6079,6 +11131,42 @@
       <c r="J141" t="n">
         <v>1.115</v>
       </c>
+      <c r="K141" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M141" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="O141" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="P141" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="S141" t="n">
+        <v>142.93</v>
+      </c>
+      <c r="T141" t="n">
+        <v>181.38</v>
+      </c>
+      <c r="U141" t="n">
+        <v>9</v>
+      </c>
+      <c r="V141" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6119,6 +11207,42 @@
       <c r="J142" t="n">
         <v>1.071</v>
       </c>
+      <c r="K142" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M142" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="N142" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O142" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="P142" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R142" t="n">
+        <v>1.462</v>
+      </c>
+      <c r="S142" t="n">
+        <v>304.82</v>
+      </c>
+      <c r="T142" t="n">
+        <v>198.22</v>
+      </c>
+      <c r="U142" t="n">
+        <v>30</v>
+      </c>
+      <c r="V142" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6159,6 +11283,42 @@
       <c r="J143" t="n">
         <v>1.071</v>
       </c>
+      <c r="K143" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M143" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="N143" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="P143" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R143" t="n">
+        <v>1.462</v>
+      </c>
+      <c r="S143" t="n">
+        <v>289.31</v>
+      </c>
+      <c r="T143" t="n">
+        <v>267.14</v>
+      </c>
+      <c r="U143" t="n">
+        <v>20</v>
+      </c>
+      <c r="V143" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6199,6 +11359,42 @@
       <c r="J144" t="n">
         <v>1.071</v>
       </c>
+      <c r="K144" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M144" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="O144" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P144" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="S144" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="T144" t="n">
+        <v>225.78</v>
+      </c>
+      <c r="U144" t="n">
+        <v>15</v>
+      </c>
+      <c r="V144" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6239,6 +11435,42 @@
       <c r="J145" t="n">
         <v>1.071</v>
       </c>
+      <c r="K145" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M145" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O145" t="n">
+        <v>-3.55</v>
+      </c>
+      <c r="P145" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="S145" t="n">
+        <v>215.61</v>
+      </c>
+      <c r="T145" t="n">
+        <v>300.92</v>
+      </c>
+      <c r="U145" t="n">
+        <v>11</v>
+      </c>
+      <c r="V145" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6279,6 +11511,42 @@
       <c r="J146" t="n">
         <v>1.071</v>
       </c>
+      <c r="K146" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M146" t="n">
+        <v>75</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="O146" t="n">
+        <v>-5.73</v>
+      </c>
+      <c r="P146" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="S146" t="n">
+        <v>162.85</v>
+      </c>
+      <c r="T146" t="n">
+        <v>300.4</v>
+      </c>
+      <c r="U146" t="n">
+        <v>13</v>
+      </c>
+      <c r="V146" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6311,7 +11579,7 @@
         <v>1.57</v>
       </c>
       <c r="H147" t="n">
-        <v>0.9879999999999999</v>
+        <v>0.9880000000000001</v>
       </c>
       <c r="I147" t="n">
         <v>24</v>
@@ -6319,6 +11587,42 @@
       <c r="J147" t="n">
         <v>1.071</v>
       </c>
+      <c r="K147" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M147" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N147" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O147" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="P147" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R147" t="n">
+        <v>1.455</v>
+      </c>
+      <c r="S147" t="n">
+        <v>467.18</v>
+      </c>
+      <c r="T147" t="n">
+        <v>259.31</v>
+      </c>
+      <c r="U147" t="n">
+        <v>21</v>
+      </c>
+      <c r="V147" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6351,7 +11655,7 @@
         <v>1.28</v>
       </c>
       <c r="H148" t="n">
-        <v>0.9879999999999999</v>
+        <v>0.9880000000000001</v>
       </c>
       <c r="I148" t="n">
         <v>24</v>
@@ -6359,6 +11663,42 @@
       <c r="J148" t="n">
         <v>1.071</v>
       </c>
+      <c r="K148" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M148" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N148" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O148" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="P148" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R148" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="S148" t="n">
+        <v>328.75</v>
+      </c>
+      <c r="T148" t="n">
+        <v>216.41</v>
+      </c>
+      <c r="U148" t="n">
+        <v>16</v>
+      </c>
+      <c r="V148" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6391,7 +11731,7 @@
         <v>0.89</v>
       </c>
       <c r="H149" t="n">
-        <v>0.9879999999999999</v>
+        <v>0.9880000000000001</v>
       </c>
       <c r="I149" t="n">
         <v>24</v>
@@ -6399,6 +11739,42 @@
       <c r="J149" t="n">
         <v>1.071</v>
       </c>
+      <c r="K149" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M149" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O149" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="P149" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="S149" t="n">
+        <v>204.05</v>
+      </c>
+      <c r="T149" t="n">
+        <v>237.61</v>
+      </c>
+      <c r="U149" t="n">
+        <v>14</v>
+      </c>
+      <c r="V149" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6431,7 +11807,7 @@
         <v>0.6</v>
       </c>
       <c r="H150" t="n">
-        <v>0.9879999999999999</v>
+        <v>0.9880000000000001</v>
       </c>
       <c r="I150" t="n">
         <v>24</v>
@@ -6439,6 +11815,42 @@
       <c r="J150" t="n">
         <v>1.071</v>
       </c>
+      <c r="K150" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M150" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O150" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="P150" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="S150" t="n">
+        <v>124.11</v>
+      </c>
+      <c r="T150" t="n">
+        <v>250.88</v>
+      </c>
+      <c r="U150" t="n">
+        <v>7</v>
+      </c>
+      <c r="V150" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6471,7 +11883,7 @@
         <v>0.6</v>
       </c>
       <c r="H151" t="n">
-        <v>0.9879999999999999</v>
+        <v>0.9880000000000001</v>
       </c>
       <c r="I151" t="n">
         <v>24</v>
@@ -6479,6 +11891,42 @@
       <c r="J151" t="n">
         <v>1.071</v>
       </c>
+      <c r="K151" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M151" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="N151" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="O151" t="n">
+        <v>-5.38</v>
+      </c>
+      <c r="P151" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="S151" t="n">
+        <v>168.3</v>
+      </c>
+      <c r="T151" t="n">
+        <v>297.3</v>
+      </c>
+      <c r="U151" t="n">
+        <v>12</v>
+      </c>
+      <c r="V151" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6511,7 +11959,7 @@
         <v>0.8</v>
       </c>
       <c r="H152" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I152" t="n">
         <v>15</v>
@@ -6519,6 +11967,42 @@
       <c r="J152" t="n">
         <v>1.065</v>
       </c>
+      <c r="K152" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M152" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="O152" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="P152" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R152" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S152" t="n">
+        <v>144.91</v>
+      </c>
+      <c r="T152" t="n">
+        <v>186.85</v>
+      </c>
+      <c r="U152" t="n">
+        <v>7</v>
+      </c>
+      <c r="V152" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6551,7 +12035,7 @@
         <v>0.78</v>
       </c>
       <c r="H153" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I153" t="n">
         <v>15</v>
@@ -6559,6 +12043,42 @@
       <c r="J153" t="n">
         <v>1.065</v>
       </c>
+      <c r="K153" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="M153" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="N153" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="P153" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="R153" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S153" t="n">
+        <v>146.62</v>
+      </c>
+      <c r="T153" t="n">
+        <v>144.64</v>
+      </c>
+      <c r="U153" t="n">
+        <v>7</v>
+      </c>
+      <c r="V153" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6591,7 +12111,7 @@
         <v>0.68</v>
       </c>
       <c r="H154" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I154" t="n">
         <v>15</v>
@@ -6599,6 +12119,42 @@
       <c r="J154" t="n">
         <v>1.065</v>
       </c>
+      <c r="K154" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="M154" t="n">
+        <v>60</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="O154" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="P154" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="R154" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S154" t="n">
+        <v>170.74</v>
+      </c>
+      <c r="T154" t="n">
+        <v>185.09</v>
+      </c>
+      <c r="U154" t="n">
+        <v>6</v>
+      </c>
+      <c r="V154" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6631,7 +12187,7 @@
         <v>0.28</v>
       </c>
       <c r="H155" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I155" t="n">
         <v>15</v>
@@ -6639,6 +12195,42 @@
       <c r="J155" t="n">
         <v>1.065</v>
       </c>
+      <c r="K155" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="M155" t="n">
+        <v>40</v>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>-8.619999999999999</v>
+      </c>
+      <c r="P155" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="n">
+        <v>44.49</v>
+      </c>
+      <c r="T155" t="n">
+        <v>173.82</v>
+      </c>
+      <c r="U155" t="n">
+        <v>3</v>
+      </c>
+      <c r="V155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6671,7 +12263,7 @@
         <v>0.26</v>
       </c>
       <c r="H156" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I156" t="n">
         <v>15</v>
@@ -6679,6 +12271,42 @@
       <c r="J156" t="n">
         <v>1.065</v>
       </c>
+      <c r="K156" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="M156" t="n">
+        <v>40</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>-12.63</v>
+      </c>
+      <c r="P156" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="n">
+        <v>42.41</v>
+      </c>
+      <c r="T156" t="n">
+        <v>231.92</v>
+      </c>
+      <c r="U156" t="n">
+        <v>2</v>
+      </c>
+      <c r="V156" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6719,6 +12347,42 @@
       <c r="J157" t="n">
         <v>1.065</v>
       </c>
+      <c r="K157" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M157" t="n">
+        <v>100</v>
+      </c>
+      <c r="N157" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O157" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="P157" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="R157" t="n">
+        <v>1</v>
+      </c>
+      <c r="S157" t="n">
+        <v>246.3</v>
+      </c>
+      <c r="T157" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="U157" t="n">
+        <v>17</v>
+      </c>
+      <c r="V157" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6759,6 +12423,42 @@
       <c r="J158" t="n">
         <v>1.065</v>
       </c>
+      <c r="K158" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M158" t="n">
+        <v>100</v>
+      </c>
+      <c r="N158" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O158" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="P158" t="n">
+        <v>112</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="R158" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="S158" t="n">
+        <v>244.2</v>
+      </c>
+      <c r="T158" t="n">
+        <v>81.06</v>
+      </c>
+      <c r="U158" t="n">
+        <v>17</v>
+      </c>
+      <c r="V158" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6799,6 +12499,42 @@
       <c r="J159" t="n">
         <v>1.065</v>
       </c>
+      <c r="K159" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M159" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="O159" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="P159" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="S159" t="n">
+        <v>214.87</v>
+      </c>
+      <c r="T159" t="n">
+        <v>167.98</v>
+      </c>
+      <c r="U159" t="n">
+        <v>13</v>
+      </c>
+      <c r="V159" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6839,6 +12575,42 @@
       <c r="J160" t="n">
         <v>1.065</v>
       </c>
+      <c r="K160" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M160" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="O160" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="P160" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="S160" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="T160" t="n">
+        <v>120.96</v>
+      </c>
+      <c r="U160" t="n">
+        <v>11</v>
+      </c>
+      <c r="V160" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6879,6 +12651,42 @@
       <c r="J161" t="n">
         <v>1.065</v>
       </c>
+      <c r="K161" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M161" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P161" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="S161" t="n">
+        <v>113.18</v>
+      </c>
+      <c r="T161" t="n">
+        <v>105.41</v>
+      </c>
+      <c r="U161" t="n">
+        <v>8</v>
+      </c>
+      <c r="V161" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6919,6 +12727,42 @@
       <c r="J162" t="n">
         <v>1.072</v>
       </c>
+      <c r="K162" t="n">
+        <v>1</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M162" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="N162" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="O162" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="P162" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R162" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="S162" t="n">
+        <v>213.21</v>
+      </c>
+      <c r="T162" t="n">
+        <v>96.31</v>
+      </c>
+      <c r="U162" t="n">
+        <v>19</v>
+      </c>
+      <c r="V162" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6959,6 +12803,42 @@
       <c r="J163" t="n">
         <v>1.072</v>
       </c>
+      <c r="K163" t="n">
+        <v>1</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M163" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="N163" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="O163" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="P163" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R163" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="S163" t="n">
+        <v>139.57</v>
+      </c>
+      <c r="T163" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="U163" t="n">
+        <v>18</v>
+      </c>
+      <c r="V163" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6999,6 +12879,42 @@
       <c r="J164" t="n">
         <v>1.072</v>
       </c>
+      <c r="K164" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M164" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="N164" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O164" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P164" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R164" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="S164" t="n">
+        <v>167.94</v>
+      </c>
+      <c r="T164" t="n">
+        <v>124.26</v>
+      </c>
+      <c r="U164" t="n">
+        <v>17</v>
+      </c>
+      <c r="V164" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7039,6 +12955,42 @@
       <c r="J165" t="n">
         <v>1.072</v>
       </c>
+      <c r="K165" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M165" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="O165" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P165" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="S165" t="n">
+        <v>226.34</v>
+      </c>
+      <c r="T165" t="n">
+        <v>184.56</v>
+      </c>
+      <c r="U165" t="n">
+        <v>11</v>
+      </c>
+      <c r="V165" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7079,6 +13031,42 @@
       <c r="J166" t="n">
         <v>1.072</v>
       </c>
+      <c r="K166" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M166" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P166" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="S166" t="n">
+        <v>153.74</v>
+      </c>
+      <c r="T166" t="n">
+        <v>147.55</v>
+      </c>
+      <c r="U166" t="n">
+        <v>9</v>
+      </c>
+      <c r="V166" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7119,6 +13107,42 @@
       <c r="J167" t="n">
         <v>1.072</v>
       </c>
+      <c r="K167" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M167" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="N167" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O167" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="P167" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R167" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="S167" t="n">
+        <v>175.79</v>
+      </c>
+      <c r="T167" t="n">
+        <v>156.26</v>
+      </c>
+      <c r="U167" t="n">
+        <v>17</v>
+      </c>
+      <c r="V167" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7159,6 +13183,42 @@
       <c r="J168" t="n">
         <v>1.072</v>
       </c>
+      <c r="K168" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M168" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="O168" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="P168" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>1</v>
+      </c>
+      <c r="R168" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="S168" t="n">
+        <v>127.38</v>
+      </c>
+      <c r="T168" t="n">
+        <v>150.35</v>
+      </c>
+      <c r="U168" t="n">
+        <v>13</v>
+      </c>
+      <c r="V168" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7199,6 +13259,42 @@
       <c r="J169" t="n">
         <v>1.072</v>
       </c>
+      <c r="K169" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M169" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="P169" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="S169" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="T169" t="n">
+        <v>207.79</v>
+      </c>
+      <c r="U169" t="n">
+        <v>9</v>
+      </c>
+      <c r="V169" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7239,6 +13335,42 @@
       <c r="J170" t="n">
         <v>1.072</v>
       </c>
+      <c r="K170" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L170" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M170" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="O170" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="P170" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="R170" t="n">
+        <v>1</v>
+      </c>
+      <c r="S170" t="n">
+        <v>93.70999999999999</v>
+      </c>
+      <c r="T170" t="n">
+        <v>228.59</v>
+      </c>
+      <c r="U170" t="n">
+        <v>8</v>
+      </c>
+      <c r="V170" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7279,6 +13411,42 @@
       <c r="J171" t="n">
         <v>1.072</v>
       </c>
+      <c r="K171" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M171" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="N171" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="O171" t="n">
+        <v>-6.22</v>
+      </c>
+      <c r="P171" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0</v>
+      </c>
+      <c r="S171" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="T171" t="n">
+        <v>157.85</v>
+      </c>
+      <c r="U171" t="n">
+        <v>3</v>
+      </c>
+      <c r="V171" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7319,6 +13487,42 @@
       <c r="J172" t="n">
         <v>1.044</v>
       </c>
+      <c r="K172" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L172" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M172" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="N172" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O172" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="P172" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="S172" t="n">
+        <v>199</v>
+      </c>
+      <c r="T172" t="n">
+        <v>222.39</v>
+      </c>
+      <c r="U172" t="n">
+        <v>15</v>
+      </c>
+      <c r="V172" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7359,6 +13563,42 @@
       <c r="J173" t="n">
         <v>1.044</v>
       </c>
+      <c r="K173" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L173" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M173" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="N173" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="O173" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="P173" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R173" t="n">
+        <v>1</v>
+      </c>
+      <c r="S173" t="n">
+        <v>137.45</v>
+      </c>
+      <c r="T173" t="n">
+        <v>158.79</v>
+      </c>
+      <c r="U173" t="n">
+        <v>11</v>
+      </c>
+      <c r="V173" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7399,6 +13639,42 @@
       <c r="J174" t="n">
         <v>1.044</v>
       </c>
+      <c r="K174" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L174" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M174" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="N174" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="O174" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="P174" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R174" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="S174" t="n">
+        <v>172.91</v>
+      </c>
+      <c r="T174" t="n">
+        <v>191.42</v>
+      </c>
+      <c r="U174" t="n">
+        <v>12</v>
+      </c>
+      <c r="V174" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7439,6 +13715,42 @@
       <c r="J175" t="n">
         <v>1.044</v>
       </c>
+      <c r="K175" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M175" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="N175" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="O175" t="n">
+        <v>-4.17</v>
+      </c>
+      <c r="P175" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="R175" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="S175" t="n">
+        <v>141.47</v>
+      </c>
+      <c r="T175" t="n">
+        <v>220.74</v>
+      </c>
+      <c r="U175" t="n">
+        <v>9</v>
+      </c>
+      <c r="V175" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7479,6 +13791,42 @@
       <c r="J176" t="n">
         <v>1.044</v>
       </c>
+      <c r="K176" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L176" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M176" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="N176" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O176" t="n">
+        <v>-7.46</v>
+      </c>
+      <c r="P176" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="R176" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="S176" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="T176" t="n">
+        <v>246.57</v>
+      </c>
+      <c r="U176" t="n">
+        <v>9</v>
+      </c>
+      <c r="V176" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7519,6 +13867,42 @@
       <c r="J177" t="n">
         <v>1.044</v>
       </c>
+      <c r="K177" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L177" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M177" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="N177" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="O177" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="P177" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R177" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="S177" t="n">
+        <v>291.55</v>
+      </c>
+      <c r="T177" t="n">
+        <v>153.15</v>
+      </c>
+      <c r="U177" t="n">
+        <v>15</v>
+      </c>
+      <c r="V177" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7559,6 +13943,42 @@
       <c r="J178" t="n">
         <v>1.044</v>
       </c>
+      <c r="K178" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M178" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="N178" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="O178" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="P178" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R178" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="S178" t="n">
+        <v>231.07</v>
+      </c>
+      <c r="T178" t="n">
+        <v>134.69</v>
+      </c>
+      <c r="U178" t="n">
+        <v>16</v>
+      </c>
+      <c r="V178" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7599,6 +14019,42 @@
       <c r="J179" t="n">
         <v>1.044</v>
       </c>
+      <c r="K179" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L179" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M179" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O179" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="P179" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R179" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="S179" t="n">
+        <v>171.02</v>
+      </c>
+      <c r="T179" t="n">
+        <v>117.19</v>
+      </c>
+      <c r="U179" t="n">
+        <v>15</v>
+      </c>
+      <c r="V179" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7639,6 +14095,42 @@
       <c r="J180" t="n">
         <v>1.044</v>
       </c>
+      <c r="K180" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M180" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="N180" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="O180" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="P180" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R180" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="S180" t="n">
+        <v>224.72</v>
+      </c>
+      <c r="T180" t="n">
+        <v>182.67</v>
+      </c>
+      <c r="U180" t="n">
+        <v>12</v>
+      </c>
+      <c r="V180" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7679,6 +14171,42 @@
       <c r="J181" t="n">
         <v>1.044</v>
       </c>
+      <c r="K181" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M181" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="N181" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="O181" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="P181" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R181" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="S181" t="n">
+        <v>121.59</v>
+      </c>
+      <c r="T181" t="n">
+        <v>167.86</v>
+      </c>
+      <c r="U181" t="n">
+        <v>10</v>
+      </c>
+      <c r="V181" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7719,6 +14247,42 @@
       <c r="J182" t="n">
         <v>1.06</v>
       </c>
+      <c r="K182" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L182" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M182" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N182" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O182" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="P182" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R182" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S182" t="n">
+        <v>368.56</v>
+      </c>
+      <c r="T182" t="n">
+        <v>282.76</v>
+      </c>
+      <c r="U182" t="n">
+        <v>28</v>
+      </c>
+      <c r="V182" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7759,6 +14323,42 @@
       <c r="J183" t="n">
         <v>1.06</v>
       </c>
+      <c r="K183" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L183" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M183" t="n">
+        <v>70</v>
+      </c>
+      <c r="N183" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="O183" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="P183" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="R183" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="S183" t="n">
+        <v>291.84</v>
+      </c>
+      <c r="T183" t="n">
+        <v>327.41</v>
+      </c>
+      <c r="U183" t="n">
+        <v>21</v>
+      </c>
+      <c r="V183" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7799,6 +14399,42 @@
       <c r="J184" t="n">
         <v>1.06</v>
       </c>
+      <c r="K184" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L184" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M184" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="N184" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="O184" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P184" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="R184" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="S184" t="n">
+        <v>304.21</v>
+      </c>
+      <c r="T184" t="n">
+        <v>267.69</v>
+      </c>
+      <c r="U184" t="n">
+        <v>19</v>
+      </c>
+      <c r="V184" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7839,6 +14475,42 @@
       <c r="J185" t="n">
         <v>1.06</v>
       </c>
+      <c r="K185" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L185" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M185" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="N185" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="O185" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="P185" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="R185" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="S185" t="n">
+        <v>310.56</v>
+      </c>
+      <c r="T185" t="n">
+        <v>374.08</v>
+      </c>
+      <c r="U185" t="n">
+        <v>19</v>
+      </c>
+      <c r="V185" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7879,6 +14551,42 @@
       <c r="J186" t="n">
         <v>1.06</v>
       </c>
+      <c r="K186" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L186" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M186" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N186" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O186" t="n">
+        <v>-5.73</v>
+      </c>
+      <c r="P186" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="R186" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="S186" t="n">
+        <v>218.01</v>
+      </c>
+      <c r="T186" t="n">
+        <v>389.88</v>
+      </c>
+      <c r="U186" t="n">
+        <v>19</v>
+      </c>
+      <c r="V186" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7919,6 +14627,42 @@
       <c r="J187" t="n">
         <v>1.06</v>
       </c>
+      <c r="K187" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L187" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M187" t="n">
+        <v>70</v>
+      </c>
+      <c r="N187" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O187" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="P187" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R187" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="S187" t="n">
+        <v>400.41</v>
+      </c>
+      <c r="T187" t="n">
+        <v>330.82</v>
+      </c>
+      <c r="U187" t="n">
+        <v>20</v>
+      </c>
+      <c r="V187" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7959,6 +14703,42 @@
       <c r="J188" t="n">
         <v>1.06</v>
       </c>
+      <c r="K188" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L188" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M188" t="n">
+        <v>70</v>
+      </c>
+      <c r="N188" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="O188" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P188" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="R188" t="n">
+        <v>1</v>
+      </c>
+      <c r="S188" t="n">
+        <v>318.8</v>
+      </c>
+      <c r="T188" t="n">
+        <v>237.44</v>
+      </c>
+      <c r="U188" t="n">
+        <v>20</v>
+      </c>
+      <c r="V188" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7999,6 +14779,42 @@
       <c r="J189" t="n">
         <v>1.06</v>
       </c>
+      <c r="K189" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L189" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M189" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="N189" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="O189" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="P189" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R189" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S189" t="n">
+        <v>360.2</v>
+      </c>
+      <c r="T189" t="n">
+        <v>287.35</v>
+      </c>
+      <c r="U189" t="n">
+        <v>21</v>
+      </c>
+      <c r="V189" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8039,6 +14855,42 @@
       <c r="J190" t="n">
         <v>1.06</v>
       </c>
+      <c r="K190" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L190" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M190" t="n">
+        <v>80</v>
+      </c>
+      <c r="N190" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="P190" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R190" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="S190" t="n">
+        <v>308.73</v>
+      </c>
+      <c r="T190" t="n">
+        <v>284.98</v>
+      </c>
+      <c r="U190" t="n">
+        <v>21</v>
+      </c>
+      <c r="V190" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8079,6 +14931,42 @@
       <c r="J191" t="n">
         <v>1.06</v>
       </c>
+      <c r="K191" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M191" t="n">
+        <v>70</v>
+      </c>
+      <c r="N191" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="O191" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="P191" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R191" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="S191" t="n">
+        <v>253.68</v>
+      </c>
+      <c r="T191" t="n">
+        <v>352.57</v>
+      </c>
+      <c r="U191" t="n">
+        <v>18</v>
+      </c>
+      <c r="V191" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8119,6 +15007,42 @@
       <c r="J192" t="n">
         <v>1.03</v>
       </c>
+      <c r="K192" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M192" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="N192" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="P192" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R192" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="S192" t="n">
+        <v>256.12</v>
+      </c>
+      <c r="T192" t="n">
+        <v>240.39</v>
+      </c>
+      <c r="U192" t="n">
+        <v>26</v>
+      </c>
+      <c r="V192" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8159,6 +15083,42 @@
       <c r="J193" t="n">
         <v>1.03</v>
       </c>
+      <c r="K193" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M193" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="N193" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="O193" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="P193" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R193" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="S193" t="n">
+        <v>239.4</v>
+      </c>
+      <c r="T193" t="n">
+        <v>184.05</v>
+      </c>
+      <c r="U193" t="n">
+        <v>22</v>
+      </c>
+      <c r="V193" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8199,6 +15159,42 @@
       <c r="J194" t="n">
         <v>1.03</v>
       </c>
+      <c r="K194" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L194" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M194" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="N194" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="O194" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P194" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R194" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="S194" t="n">
+        <v>241.57</v>
+      </c>
+      <c r="T194" t="n">
+        <v>190.06</v>
+      </c>
+      <c r="U194" t="n">
+        <v>18</v>
+      </c>
+      <c r="V194" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8239,6 +15235,42 @@
       <c r="J195" t="n">
         <v>1.03</v>
       </c>
+      <c r="K195" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L195" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M195" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="N195" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="O195" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="P195" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="R195" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="S195" t="n">
+        <v>184.44</v>
+      </c>
+      <c r="T195" t="n">
+        <v>251.21</v>
+      </c>
+      <c r="U195" t="n">
+        <v>19</v>
+      </c>
+      <c r="V195" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -8279,6 +15311,42 @@
       <c r="J196" t="n">
         <v>1.03</v>
       </c>
+      <c r="K196" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L196" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M196" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N196" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="O196" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="P196" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="R196" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="S196" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="T196" t="n">
+        <v>170.24</v>
+      </c>
+      <c r="U196" t="n">
+        <v>8</v>
+      </c>
+      <c r="V196" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -8311,7 +15379,7 @@
         <v>1.25</v>
       </c>
       <c r="H197" t="n">
-        <v>0.8620000000000001</v>
+        <v>0.8619999999999999</v>
       </c>
       <c r="I197" t="n">
         <v>24</v>
@@ -8319,6 +15387,42 @@
       <c r="J197" t="n">
         <v>1.03</v>
       </c>
+      <c r="K197" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M197" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="N197" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O197" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P197" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R197" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="S197" t="n">
+        <v>298</v>
+      </c>
+      <c r="T197" t="n">
+        <v>208.58</v>
+      </c>
+      <c r="U197" t="n">
+        <v>19</v>
+      </c>
+      <c r="V197" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8351,7 +15455,7 @@
         <v>1.03</v>
       </c>
       <c r="H198" t="n">
-        <v>0.8620000000000001</v>
+        <v>0.8619999999999999</v>
       </c>
       <c r="I198" t="n">
         <v>24</v>
@@ -8359,6 +15463,42 @@
       <c r="J198" t="n">
         <v>1.03</v>
       </c>
+      <c r="K198" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M198" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="N198" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O198" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="P198" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="R198" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="S198" t="n">
+        <v>220.63</v>
+      </c>
+      <c r="T198" t="n">
+        <v>153.89</v>
+      </c>
+      <c r="U198" t="n">
+        <v>16</v>
+      </c>
+      <c r="V198" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8391,7 +15531,7 @@
         <v>0.84</v>
       </c>
       <c r="H199" t="n">
-        <v>0.8620000000000001</v>
+        <v>0.8619999999999999</v>
       </c>
       <c r="I199" t="n">
         <v>24</v>
@@ -8399,6 +15539,42 @@
       <c r="J199" t="n">
         <v>1.03</v>
       </c>
+      <c r="K199" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M199" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="N199" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P199" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="R199" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="S199" t="n">
+        <v>235.27</v>
+      </c>
+      <c r="T199" t="n">
+        <v>225.28</v>
+      </c>
+      <c r="U199" t="n">
+        <v>13</v>
+      </c>
+      <c r="V199" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8431,7 +15607,7 @@
         <v>0.6</v>
       </c>
       <c r="H200" t="n">
-        <v>0.8620000000000001</v>
+        <v>0.8619999999999999</v>
       </c>
       <c r="I200" t="n">
         <v>24</v>
@@ -8439,6 +15615,42 @@
       <c r="J200" t="n">
         <v>1.03</v>
       </c>
+      <c r="K200" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M200" t="n">
+        <v>50</v>
+      </c>
+      <c r="N200" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="P200" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R200" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="S200" t="n">
+        <v>142.03</v>
+      </c>
+      <c r="T200" t="n">
+        <v>180.54</v>
+      </c>
+      <c r="U200" t="n">
+        <v>5</v>
+      </c>
+      <c r="V200" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8471,7 +15683,7 @@
         <v>0.59</v>
       </c>
       <c r="H201" t="n">
-        <v>0.8620000000000001</v>
+        <v>0.8619999999999999</v>
       </c>
       <c r="I201" t="n">
         <v>24</v>
@@ -8479,6 +15691,42 @@
       <c r="J201" t="n">
         <v>1.03</v>
       </c>
+      <c r="K201" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M201" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="N201" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O201" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="P201" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="R201" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="S201" t="n">
+        <v>140.02</v>
+      </c>
+      <c r="T201" t="n">
+        <v>247.02</v>
+      </c>
+      <c r="U201" t="n">
+        <v>9</v>
+      </c>
+      <c r="V201" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8511,7 +15759,7 @@
         <v>0.97</v>
       </c>
       <c r="H202" t="n">
-        <v>0.7899999999999998</v>
+        <v>0.79</v>
       </c>
       <c r="I202" t="n">
         <v>21</v>
@@ -8519,6 +15767,42 @@
       <c r="J202" t="n">
         <v>1.041</v>
       </c>
+      <c r="K202" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L202" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M202" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N202" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="O202" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P202" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="R202" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S202" t="n">
+        <v>198.64</v>
+      </c>
+      <c r="T202" t="n">
+        <v>153.33</v>
+      </c>
+      <c r="U202" t="n">
+        <v>12</v>
+      </c>
+      <c r="V202" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8551,7 +15835,7 @@
         <v>0.89</v>
       </c>
       <c r="H203" t="n">
-        <v>0.7899999999999998</v>
+        <v>0.79</v>
       </c>
       <c r="I203" t="n">
         <v>21</v>
@@ -8559,6 +15843,42 @@
       <c r="J203" t="n">
         <v>1.041</v>
       </c>
+      <c r="K203" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L203" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M203" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="N203" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="O203" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="P203" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="R203" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S203" t="n">
+        <v>218.4</v>
+      </c>
+      <c r="T203" t="n">
+        <v>245.89</v>
+      </c>
+      <c r="U203" t="n">
+        <v>13</v>
+      </c>
+      <c r="V203" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -8591,7 +15911,7 @@
         <v>0.88</v>
       </c>
       <c r="H204" t="n">
-        <v>0.7899999999999998</v>
+        <v>0.79</v>
       </c>
       <c r="I204" t="n">
         <v>21</v>
@@ -8599,6 +15919,42 @@
       <c r="J204" t="n">
         <v>1.041</v>
       </c>
+      <c r="K204" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L204" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M204" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="N204" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="O204" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P204" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R204" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="S204" t="n">
+        <v>219.73</v>
+      </c>
+      <c r="T204" t="n">
+        <v>196.97</v>
+      </c>
+      <c r="U204" t="n">
+        <v>11</v>
+      </c>
+      <c r="V204" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8631,7 +15987,7 @@
         <v>0.74</v>
       </c>
       <c r="H205" t="n">
-        <v>0.7899999999999998</v>
+        <v>0.79</v>
       </c>
       <c r="I205" t="n">
         <v>21</v>
@@ -8639,6 +15995,42 @@
       <c r="J205" t="n">
         <v>1.041</v>
       </c>
+      <c r="K205" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L205" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M205" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="N205" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="O205" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="P205" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="R205" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="S205" t="n">
+        <v>173.59</v>
+      </c>
+      <c r="T205" t="n">
+        <v>237.76</v>
+      </c>
+      <c r="U205" t="n">
+        <v>8</v>
+      </c>
+      <c r="V205" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -8671,7 +16063,7 @@
         <v>0.47</v>
       </c>
       <c r="H206" t="n">
-        <v>0.7899999999999998</v>
+        <v>0.79</v>
       </c>
       <c r="I206" t="n">
         <v>21</v>
@@ -8679,6 +16071,42 @@
       <c r="J206" t="n">
         <v>1.041</v>
       </c>
+      <c r="K206" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L206" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M206" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="N206" t="n">
+        <v>0</v>
+      </c>
+      <c r="O206" t="n">
+        <v>-5.69</v>
+      </c>
+      <c r="P206" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="R206" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S206" t="n">
+        <v>190.26</v>
+      </c>
+      <c r="T206" t="n">
+        <v>309.84</v>
+      </c>
+      <c r="U206" t="n">
+        <v>6</v>
+      </c>
+      <c r="V206" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -8719,6 +16147,42 @@
       <c r="J207" t="n">
         <v>1.041</v>
       </c>
+      <c r="K207" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M207" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="N207" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O207" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="P207" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R207" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="S207" t="n">
+        <v>331.41</v>
+      </c>
+      <c r="T207" t="n">
+        <v>230.82</v>
+      </c>
+      <c r="U207" t="n">
+        <v>23</v>
+      </c>
+      <c r="V207" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -8759,6 +16223,42 @@
       <c r="J208" t="n">
         <v>1.041</v>
       </c>
+      <c r="K208" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M208" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="N208" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="O208" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="P208" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="S208" t="n">
+        <v>239.42</v>
+      </c>
+      <c r="T208" t="n">
+        <v>169.47</v>
+      </c>
+      <c r="U208" t="n">
+        <v>16</v>
+      </c>
+      <c r="V208" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8799,6 +16299,42 @@
       <c r="J209" t="n">
         <v>1.041</v>
       </c>
+      <c r="K209" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M209" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="N209" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O209" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="P209" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R209" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="S209" t="n">
+        <v>199.03</v>
+      </c>
+      <c r="T209" t="n">
+        <v>213.97</v>
+      </c>
+      <c r="U209" t="n">
+        <v>17</v>
+      </c>
+      <c r="V209" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -8839,6 +16375,42 @@
       <c r="J210" t="n">
         <v>1.041</v>
       </c>
+      <c r="K210" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M210" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="N210" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="O210" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="P210" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="S210" t="n">
+        <v>200.97</v>
+      </c>
+      <c r="T210" t="n">
+        <v>163.56</v>
+      </c>
+      <c r="U210" t="n">
+        <v>12</v>
+      </c>
+      <c r="V210" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8879,6 +16451,42 @@
       <c r="J211" t="n">
         <v>1.041</v>
       </c>
+      <c r="K211" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M211" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="N211" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="O211" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="P211" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="S211" t="n">
+        <v>172.94</v>
+      </c>
+      <c r="T211" t="n">
+        <v>235.62</v>
+      </c>
+      <c r="U211" t="n">
+        <v>14</v>
+      </c>
+      <c r="V211" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8919,6 +16527,42 @@
       <c r="J212" t="n">
         <v>1.099</v>
       </c>
+      <c r="K212" t="n">
+        <v>1</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M212" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="N212" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O212" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="P212" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R212" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="S212" t="n">
+        <v>299.86</v>
+      </c>
+      <c r="T212" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="U212" t="n">
+        <v>21</v>
+      </c>
+      <c r="V212" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8959,6 +16603,42 @@
       <c r="J213" t="n">
         <v>1.099</v>
       </c>
+      <c r="K213" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M213" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="N213" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="O213" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="P213" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R213" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="S213" t="n">
+        <v>263.78</v>
+      </c>
+      <c r="T213" t="n">
+        <v>192.73</v>
+      </c>
+      <c r="U213" t="n">
+        <v>19</v>
+      </c>
+      <c r="V213" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8999,6 +16679,42 @@
       <c r="J214" t="n">
         <v>1.099</v>
       </c>
+      <c r="K214" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L214" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M214" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="N214" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="O214" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="P214" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R214" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="S214" t="n">
+        <v>215.01</v>
+      </c>
+      <c r="T214" t="n">
+        <v>177.72</v>
+      </c>
+      <c r="U214" t="n">
+        <v>14</v>
+      </c>
+      <c r="V214" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -9039,6 +16755,42 @@
       <c r="J215" t="n">
         <v>1.099</v>
       </c>
+      <c r="K215" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M215" t="n">
+        <v>81</v>
+      </c>
+      <c r="N215" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="P215" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R215" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="S215" t="n">
+        <v>255.77</v>
+      </c>
+      <c r="T215" t="n">
+        <v>240.22</v>
+      </c>
+      <c r="U215" t="n">
+        <v>17</v>
+      </c>
+      <c r="V215" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -9079,6 +16831,42 @@
       <c r="J216" t="n">
         <v>1.099</v>
       </c>
+      <c r="K216" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M216" t="n">
+        <v>81</v>
+      </c>
+      <c r="N216" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="O216" t="n">
+        <v>-3.17</v>
+      </c>
+      <c r="P216" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="R216" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="S216" t="n">
+        <v>235</v>
+      </c>
+      <c r="T216" t="n">
+        <v>301.65</v>
+      </c>
+      <c r="U216" t="n">
+        <v>13</v>
+      </c>
+      <c r="V216" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -9119,6 +16907,42 @@
       <c r="J217" t="n">
         <v>1.099</v>
       </c>
+      <c r="K217" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M217" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="N217" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O217" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="P217" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R217" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="S217" t="n">
+        <v>333.21</v>
+      </c>
+      <c r="T217" t="n">
+        <v>223.45</v>
+      </c>
+      <c r="U217" t="n">
+        <v>16</v>
+      </c>
+      <c r="V217" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -9159,6 +16983,42 @@
       <c r="J218" t="n">
         <v>1.099</v>
       </c>
+      <c r="K218" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M218" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="N218" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O218" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P218" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="R218" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="S218" t="n">
+        <v>268.32</v>
+      </c>
+      <c r="T218" t="n">
+        <v>243.31</v>
+      </c>
+      <c r="U218" t="n">
+        <v>15</v>
+      </c>
+      <c r="V218" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -9199,6 +17059,42 @@
       <c r="J219" t="n">
         <v>1.099</v>
       </c>
+      <c r="K219" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M219" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="N219" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="O219" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="P219" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R219" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S219" t="n">
+        <v>195.82</v>
+      </c>
+      <c r="T219" t="n">
+        <v>243.95</v>
+      </c>
+      <c r="U219" t="n">
+        <v>14</v>
+      </c>
+      <c r="V219" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -9239,6 +17135,42 @@
       <c r="J220" t="n">
         <v>1.099</v>
       </c>
+      <c r="K220" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L220" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M220" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="N220" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="O220" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="P220" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="S220" t="n">
+        <v>233.43</v>
+      </c>
+      <c r="T220" t="n">
+        <v>290.72</v>
+      </c>
+      <c r="U220" t="n">
+        <v>13</v>
+      </c>
+      <c r="V220" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -9278,6 +17210,42 @@
       </c>
       <c r="J221" t="n">
         <v>1.099</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M221" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="N221" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O221" t="n">
+        <v>-9.75</v>
+      </c>
+      <c r="P221" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S221" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="T221" t="n">
+        <v>267.99</v>
+      </c>
+      <c r="U221" t="n">
+        <v>5</v>
+      </c>
+      <c r="V221" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
